--- a/data/figures/phase3/phase3_metrics.xlsx
+++ b/data/figures/phase3/phase3_metrics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>mean_reachF</t>
   </si>
@@ -85,7 +85,13 @@
     <t>M1 M2 M3 M4</t>
   </si>
   <si>
+    <t>M2 M3 M4 M5</t>
+  </si>
+  <si>
     <t>M1 M2 M3 M4 M5</t>
+  </si>
+  <si>
+    <t>M1 M2 M3 M4 M5 M1 M2 M3 M4 M5</t>
   </si>
 </sst>
 </file>
@@ -443,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
@@ -746,57 +752,175 @@
         <v>23</v>
       </c>
       <c r="B6">
+        <v>83.56</v>
+      </c>
+      <c r="C6">
+        <v>1.061</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>99.773</v>
+      </c>
+      <c r="F6">
+        <v>0.359</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>475.333</v>
+      </c>
+      <c r="I6">
+        <v>61.849</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>2155.333</v>
+      </c>
+      <c r="L6">
+        <v>73.711</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>34</v>
+      </c>
+      <c r="O6">
+        <v>3.606</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>59</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
         <v>87.676</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>2.494</v>
       </c>
-      <c r="D6">
-        <v>20</v>
-      </c>
-      <c r="E6">
+      <c r="D7">
+        <v>20</v>
+      </c>
+      <c r="E7">
         <v>100</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>20</v>
-      </c>
-      <c r="H6">
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
         <v>610.3</v>
       </c>
-      <c r="I6">
+      <c r="I7">
         <v>102.259</v>
       </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6">
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7">
         <v>2306.05</v>
       </c>
-      <c r="L6">
+      <c r="L7">
         <v>18.698</v>
       </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-      <c r="N6">
+      <c r="M7">
+        <v>20</v>
+      </c>
+      <c r="N7">
         <v>24.8</v>
       </c>
-      <c r="O6">
+      <c r="O7">
         <v>1.765</v>
       </c>
-      <c r="P6">
-        <v>20</v>
-      </c>
-      <c r="Q6">
+      <c r="P7">
+        <v>20</v>
+      </c>
+      <c r="Q7">
         <v>58.7</v>
       </c>
-      <c r="R6">
+      <c r="R7">
         <v>0.571</v>
       </c>
-      <c r="S6">
+      <c r="S7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="C8">
+        <v>3.517</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>99.964</v>
+      </c>
+      <c r="F8">
+        <v>0.094</v>
+      </c>
+      <c r="G8">
+        <v>20</v>
+      </c>
+      <c r="H8">
+        <v>537.6</v>
+      </c>
+      <c r="I8">
+        <v>91.175</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>2215.25</v>
+      </c>
+      <c r="L8">
+        <v>51.058</v>
+      </c>
+      <c r="M8">
+        <v>20</v>
+      </c>
+      <c r="N8">
+        <v>28.75</v>
+      </c>
+      <c r="O8">
+        <v>2.789</v>
+      </c>
+      <c r="P8">
+        <v>20</v>
+      </c>
+      <c r="Q8">
+        <v>58.75</v>
+      </c>
+      <c r="R8">
+        <v>0.55</v>
+      </c>
+      <c r="S8">
         <v>20</v>
       </c>
     </row>

--- a/data/figures/phase3/phase3_metrics.xlsx
+++ b/data/figures/phase3/phase3_metrics.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Phase3_Summary" sheetId="1" r:id="rId1"/>
+    <sheet name="Phase3_Showcase" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>mean_reachF</t>
   </si>
@@ -70,28 +70,94 @@
     <t>n_t_peak_r</t>
   </si>
   <si>
+    <t>cond</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t>Condition</t>
   </si>
   <si>
-    <t>M1 M4</t>
-  </si>
-  <si>
-    <t>M2 M4</t>
-  </si>
-  <si>
-    <t>M3 M4</t>
-  </si>
-  <si>
-    <t>M1 M2 M3 M4</t>
-  </si>
-  <si>
-    <t>M2 M3 M4 M5</t>
-  </si>
-  <si>
-    <t>M1 M2 M3 M4 M5</t>
-  </si>
-  <si>
-    <t>M1 M2 M3 M4 M5 M1 M2 M3 M4 M5</t>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>MIS</t>
+  </si>
+  <si>
+    <t>REF</t>
+  </si>
+  <si>
+    <t>AS+MIS</t>
+  </si>
+  <si>
+    <t>AS+REF</t>
+  </si>
+  <si>
+    <t>REF+MIS</t>
+  </si>
+  <si>
+    <t>AS+REF+MIS</t>
+  </si>
+  <si>
+    <t>HET</t>
+  </si>
+  <si>
+    <t>SPA</t>
+  </si>
+  <si>
+    <t>HET+SPA</t>
+  </si>
+  <si>
+    <t>FULL</t>
+  </si>
+  <si>
+    <t>bl</t>
+  </si>
+  <si>
+    <t>as</t>
+  </si>
+  <si>
+    <t>mis</t>
+  </si>
+  <si>
+    <t>ref</t>
+  </si>
+  <si>
+    <t>as_mis</t>
+  </si>
+  <si>
+    <t>as_ref</t>
+  </si>
+  <si>
+    <t>ref_mis</t>
+  </si>
+  <si>
+    <t>as_ref_mis</t>
+  </si>
+  <si>
+    <t>het</t>
+  </si>
+  <si>
+    <t>spa</t>
+  </si>
+  <si>
+    <t>het_spa</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t>micro</t>
+  </si>
+  <si>
+    <t>macro</t>
   </si>
 </sst>
 </file>
@@ -449,12 +515,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -510,418 +576,791 @@
       <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>63.8</v>
+        <v>62.653</v>
       </c>
       <c r="C2">
-        <v>6.748</v>
+        <v>7.006</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>99.997</v>
       </c>
       <c r="F2">
+        <v>0.015</v>
+      </c>
+      <c r="G2">
+        <v>219</v>
+      </c>
+      <c r="H2">
+        <v>542.828</v>
+      </c>
+      <c r="I2">
+        <v>140.999</v>
+      </c>
+      <c r="J2">
+        <v>203</v>
+      </c>
+      <c r="K2">
+        <v>2154.305</v>
+      </c>
+      <c r="L2">
+        <v>31.588</v>
+      </c>
+      <c r="M2">
+        <v>203</v>
+      </c>
+      <c r="N2">
+        <v>22.892</v>
+      </c>
+      <c r="O2">
+        <v>4.008</v>
+      </c>
+      <c r="P2">
+        <v>203</v>
+      </c>
+      <c r="Q2">
+        <v>56.424</v>
+      </c>
+      <c r="R2">
+        <v>2.97</v>
+      </c>
+      <c r="S2">
+        <v>203</v>
+      </c>
+      <c r="T2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>63.289</v>
+      </c>
+      <c r="C3">
+        <v>7.695</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>20</v>
-      </c>
-      <c r="H2">
-        <v>496.95</v>
-      </c>
-      <c r="I2">
-        <v>110.524</v>
-      </c>
-      <c r="J2">
-        <v>20</v>
-      </c>
-      <c r="K2">
-        <v>2159.3</v>
-      </c>
-      <c r="L2">
-        <v>13.083</v>
-      </c>
-      <c r="M2">
-        <v>20</v>
-      </c>
-      <c r="N2">
-        <v>20.65</v>
-      </c>
-      <c r="O2">
-        <v>2.961</v>
-      </c>
-      <c r="P2">
-        <v>20</v>
-      </c>
-      <c r="Q2">
-        <v>56.05</v>
-      </c>
-      <c r="R2">
-        <v>3.471</v>
-      </c>
-      <c r="S2">
-        <v>20</v>
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>482.07</v>
+      </c>
+      <c r="I3">
+        <v>113.309</v>
+      </c>
+      <c r="J3">
+        <v>100</v>
+      </c>
+      <c r="K3">
+        <v>2155.54</v>
+      </c>
+      <c r="L3">
+        <v>13.767</v>
+      </c>
+      <c r="M3">
+        <v>100</v>
+      </c>
+      <c r="N3">
+        <v>21.09</v>
+      </c>
+      <c r="O3">
+        <v>2.723</v>
+      </c>
+      <c r="P3">
+        <v>100</v>
+      </c>
+      <c r="Q3">
+        <v>55.84</v>
+      </c>
+      <c r="R3">
+        <v>3.212</v>
+      </c>
+      <c r="S3">
+        <v>100</v>
+      </c>
+      <c r="T3" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
-        <v>69.378</v>
-      </c>
-      <c r="C3">
-        <v>4.656</v>
-      </c>
-      <c r="D3">
-        <v>20</v>
-      </c>
-      <c r="E3">
-        <v>93.614</v>
-      </c>
-      <c r="F3">
-        <v>3.901</v>
-      </c>
-      <c r="G3">
-        <v>20</v>
-      </c>
-      <c r="H3">
-        <v>976.55</v>
-      </c>
-      <c r="I3">
-        <v>121.48</v>
-      </c>
-      <c r="J3">
-        <v>20</v>
-      </c>
-      <c r="K3">
-        <v>1920.3</v>
-      </c>
-      <c r="L3">
-        <v>129.469</v>
-      </c>
-      <c r="M3">
-        <v>20</v>
-      </c>
-      <c r="N3">
-        <v>34.5</v>
-      </c>
-      <c r="O3">
-        <v>2.646</v>
-      </c>
-      <c r="P3">
-        <v>20</v>
-      </c>
-      <c r="Q3">
-        <v>59</v>
-      </c>
-      <c r="R3">
+    <row r="4" spans="1:21">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>80.45099999999999</v>
+      </c>
+      <c r="C4">
+        <v>3.805</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>99.97799999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.114</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>179.86</v>
+      </c>
+      <c r="I4">
+        <v>43.846</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4">
+        <v>2143.97</v>
+      </c>
+      <c r="L4">
+        <v>22.273</v>
+      </c>
+      <c r="M4">
+        <v>100</v>
+      </c>
+      <c r="N4">
+        <v>16.12</v>
+      </c>
+      <c r="O4">
+        <v>3.053</v>
+      </c>
+      <c r="P4">
+        <v>100</v>
+      </c>
+      <c r="Q4">
+        <v>56.51</v>
+      </c>
+      <c r="R4">
+        <v>2.267</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+      <c r="T4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>67.337</v>
+      </c>
+      <c r="C5">
+        <v>6.009</v>
+      </c>
+      <c r="D5">
+        <v>106</v>
+      </c>
+      <c r="E5">
+        <v>93.601</v>
+      </c>
+      <c r="F5">
+        <v>4.52</v>
+      </c>
+      <c r="G5">
+        <v>106</v>
+      </c>
+      <c r="H5">
+        <v>939.91</v>
+      </c>
+      <c r="I5">
+        <v>151.168</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+      <c r="K5">
+        <v>1928.91</v>
+      </c>
+      <c r="L5">
+        <v>144.574</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
+        <v>34.76</v>
+      </c>
+      <c r="O5">
+        <v>3.343</v>
+      </c>
+      <c r="P5">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>58.99</v>
+      </c>
+      <c r="R5">
+        <v>0.1</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+      <c r="T5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>81.797</v>
+      </c>
+      <c r="C6">
+        <v>3.292</v>
+      </c>
+      <c r="D6">
+        <v>60</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
         <v>0</v>
       </c>
-      <c r="S3">
-        <v>20</v>
+      <c r="G6">
+        <v>60</v>
+      </c>
+      <c r="H6">
+        <v>182.167</v>
+      </c>
+      <c r="I6">
+        <v>50.363</v>
+      </c>
+      <c r="J6">
+        <v>60</v>
+      </c>
+      <c r="K6">
+        <v>2161</v>
+      </c>
+      <c r="L6">
+        <v>15.308</v>
+      </c>
+      <c r="M6">
+        <v>60</v>
+      </c>
+      <c r="N6">
+        <v>15.117</v>
+      </c>
+      <c r="O6">
+        <v>2.285</v>
+      </c>
+      <c r="P6">
+        <v>60</v>
+      </c>
+      <c r="Q6">
+        <v>54.9</v>
+      </c>
+      <c r="R6">
+        <v>3.569</v>
+      </c>
+      <c r="S6">
+        <v>60</v>
+      </c>
+      <c r="T6" t="s">
+        <v>37</v>
+      </c>
+      <c r="U6" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4">
-        <v>79.506</v>
-      </c>
-      <c r="C4">
-        <v>4.977</v>
-      </c>
-      <c r="D4">
-        <v>20</v>
-      </c>
-      <c r="E4">
-        <v>99.97</v>
-      </c>
-      <c r="F4">
-        <v>0.074</v>
-      </c>
-      <c r="G4">
-        <v>20</v>
-      </c>
-      <c r="H4">
-        <v>183.6</v>
-      </c>
-      <c r="I4">
-        <v>41.826</v>
-      </c>
-      <c r="J4">
-        <v>20</v>
-      </c>
-      <c r="K4">
-        <v>2137.15</v>
-      </c>
-      <c r="L4">
-        <v>20.866</v>
-      </c>
-      <c r="M4">
-        <v>20</v>
-      </c>
-      <c r="N4">
-        <v>15.8</v>
-      </c>
-      <c r="O4">
-        <v>1.508</v>
-      </c>
-      <c r="P4">
-        <v>20</v>
-      </c>
-      <c r="Q4">
-        <v>56.8</v>
-      </c>
-      <c r="R4">
-        <v>2.118</v>
-      </c>
-      <c r="S4">
-        <v>20</v>
+    <row r="7" spans="1:21">
+      <c r="A7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7">
+        <v>67.68600000000001</v>
+      </c>
+      <c r="C7">
+        <v>7.027</v>
+      </c>
+      <c r="D7">
+        <v>69</v>
+      </c>
+      <c r="E7">
+        <v>97.66500000000001</v>
+      </c>
+      <c r="F7">
+        <v>2.848</v>
+      </c>
+      <c r="G7">
+        <v>69</v>
+      </c>
+      <c r="H7">
+        <v>996.333</v>
+      </c>
+      <c r="I7">
+        <v>159.119</v>
+      </c>
+      <c r="J7">
+        <v>63</v>
+      </c>
+      <c r="K7">
+        <v>2099.381</v>
+      </c>
+      <c r="L7">
+        <v>122.418</v>
+      </c>
+      <c r="M7">
+        <v>63</v>
+      </c>
+      <c r="N7">
+        <v>29.444</v>
+      </c>
+      <c r="O7">
+        <v>2.532</v>
+      </c>
+      <c r="P7">
+        <v>63</v>
+      </c>
+      <c r="Q7">
+        <v>58.984</v>
+      </c>
+      <c r="R7">
+        <v>0.126</v>
+      </c>
+      <c r="S7">
+        <v>63</v>
+      </c>
+      <c r="T7" t="s">
+        <v>38</v>
+      </c>
+      <c r="U7" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5">
-        <v>87.752</v>
-      </c>
-      <c r="C5">
-        <v>2.262</v>
-      </c>
-      <c r="D5">
-        <v>20</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>20</v>
-      </c>
-      <c r="H5">
-        <v>621.75</v>
-      </c>
-      <c r="I5">
-        <v>87.55800000000001</v>
-      </c>
-      <c r="J5">
-        <v>20</v>
-      </c>
-      <c r="K5">
-        <v>2303.55</v>
-      </c>
-      <c r="L5">
-        <v>23.874</v>
-      </c>
-      <c r="M5">
-        <v>20</v>
-      </c>
-      <c r="N5">
-        <v>25.7</v>
-      </c>
-      <c r="O5">
-        <v>2.273</v>
-      </c>
-      <c r="P5">
-        <v>20</v>
-      </c>
-      <c r="Q5">
+    <row r="8" spans="1:21">
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8">
+        <v>86.16500000000001</v>
+      </c>
+      <c r="C8">
+        <v>2.791</v>
+      </c>
+      <c r="D8">
+        <v>66</v>
+      </c>
+      <c r="E8">
+        <v>99.93899999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.142</v>
+      </c>
+      <c r="G8">
+        <v>66</v>
+      </c>
+      <c r="H8">
+        <v>575.758</v>
+      </c>
+      <c r="I8">
+        <v>102.244</v>
+      </c>
+      <c r="J8">
+        <v>66</v>
+      </c>
+      <c r="K8">
+        <v>2249.212</v>
+      </c>
+      <c r="L8">
+        <v>52.894</v>
+      </c>
+      <c r="M8">
+        <v>66</v>
+      </c>
+      <c r="N8">
+        <v>28.682</v>
+      </c>
+      <c r="O8">
+        <v>2.829</v>
+      </c>
+      <c r="P8">
+        <v>66</v>
+      </c>
+      <c r="Q8">
+        <v>58.879</v>
+      </c>
+      <c r="R8">
+        <v>0.329</v>
+      </c>
+      <c r="S8">
+        <v>66</v>
+      </c>
+      <c r="T8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>87.17</v>
+      </c>
+      <c r="C9">
+        <v>2.9</v>
+      </c>
+      <c r="D9">
+        <v>120</v>
+      </c>
+      <c r="E9">
+        <v>99.99299999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.041</v>
+      </c>
+      <c r="G9">
+        <v>120</v>
+      </c>
+      <c r="H9">
+        <v>600.167</v>
+      </c>
+      <c r="I9">
+        <v>110.938</v>
+      </c>
+      <c r="J9">
+        <v>120</v>
+      </c>
+      <c r="K9">
+        <v>2290.992</v>
+      </c>
+      <c r="L9">
+        <v>46.149</v>
+      </c>
+      <c r="M9">
+        <v>120</v>
+      </c>
+      <c r="N9">
+        <v>25.483</v>
+      </c>
+      <c r="O9">
+        <v>2.852</v>
+      </c>
+      <c r="P9">
+        <v>120</v>
+      </c>
+      <c r="Q9">
+        <v>58.683</v>
+      </c>
+      <c r="R9">
+        <v>0.635</v>
+      </c>
+      <c r="S9">
+        <v>120</v>
+      </c>
+      <c r="T9" t="s">
+        <v>40</v>
+      </c>
+      <c r="U9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10">
+        <v>64.04000000000001</v>
+      </c>
+      <c r="C10">
+        <v>7.761</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>99.998</v>
+      </c>
+      <c r="F10">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G10">
+        <v>20</v>
+      </c>
+      <c r="H10">
+        <v>466.5</v>
+      </c>
+      <c r="I10">
+        <v>150.73</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10">
+        <v>2121.9</v>
+      </c>
+      <c r="L10">
+        <v>30.731</v>
+      </c>
+      <c r="M10">
+        <v>20</v>
+      </c>
+      <c r="N10">
+        <v>25.3</v>
+      </c>
+      <c r="O10">
+        <v>3.164</v>
+      </c>
+      <c r="P10">
+        <v>20</v>
+      </c>
+      <c r="Q10">
+        <v>57.4</v>
+      </c>
+      <c r="R10">
+        <v>2.162</v>
+      </c>
+      <c r="S10">
+        <v>20</v>
+      </c>
+      <c r="T10" t="s">
+        <v>41</v>
+      </c>
+      <c r="U10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11">
+        <v>60.754</v>
+      </c>
+      <c r="C11">
+        <v>5.868</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>99.148</v>
+      </c>
+      <c r="F11">
+        <v>1.547</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11">
+        <v>427.4</v>
+      </c>
+      <c r="I11">
+        <v>102.482</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>1971</v>
+      </c>
+      <c r="L11">
+        <v>74.795</v>
+      </c>
+      <c r="M11">
+        <v>20</v>
+      </c>
+      <c r="N11">
+        <v>29.15</v>
+      </c>
+      <c r="O11">
+        <v>4.246</v>
+      </c>
+      <c r="P11">
+        <v>20</v>
+      </c>
+      <c r="Q11">
+        <v>58.6</v>
+      </c>
+      <c r="R11">
+        <v>0.883</v>
+      </c>
+      <c r="S11">
+        <v>20</v>
+      </c>
+      <c r="T11" t="s">
+        <v>42</v>
+      </c>
+      <c r="U11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12">
+        <v>61.284</v>
+      </c>
+      <c r="C12">
+        <v>5.382</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
+      </c>
+      <c r="E12">
+        <v>99.322</v>
+      </c>
+      <c r="F12">
+        <v>1.228</v>
+      </c>
+      <c r="G12">
+        <v>20</v>
+      </c>
+      <c r="H12">
+        <v>439.1</v>
+      </c>
+      <c r="I12">
+        <v>112.852</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12">
+        <v>1964.7</v>
+      </c>
+      <c r="L12">
+        <v>52.158</v>
+      </c>
+      <c r="M12">
+        <v>20</v>
+      </c>
+      <c r="N12">
+        <v>28.25</v>
+      </c>
+      <c r="O12">
+        <v>2.789</v>
+      </c>
+      <c r="P12">
+        <v>20</v>
+      </c>
+      <c r="Q12">
         <v>58.75</v>
       </c>
-      <c r="R5">
+      <c r="R12">
         <v>0.444</v>
       </c>
-      <c r="S5">
-        <v>20</v>
+      <c r="S12">
+        <v>20</v>
+      </c>
+      <c r="T12" t="s">
+        <v>43</v>
+      </c>
+      <c r="U12" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>83.56</v>
-      </c>
-      <c r="C6">
-        <v>1.061</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>99.773</v>
-      </c>
-      <c r="F6">
-        <v>0.359</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-      <c r="H6">
-        <v>475.333</v>
-      </c>
-      <c r="I6">
-        <v>61.849</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>2155.333</v>
-      </c>
-      <c r="L6">
-        <v>73.711</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-      <c r="N6">
-        <v>34</v>
-      </c>
-      <c r="O6">
-        <v>3.606</v>
-      </c>
-      <c r="P6">
-        <v>3</v>
-      </c>
-      <c r="Q6">
-        <v>59</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7">
-        <v>87.676</v>
-      </c>
-      <c r="C7">
-        <v>2.494</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>610.3</v>
-      </c>
-      <c r="I7">
-        <v>102.259</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>2306.05</v>
-      </c>
-      <c r="L7">
-        <v>18.698</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
-      </c>
-      <c r="N7">
-        <v>24.8</v>
-      </c>
-      <c r="O7">
-        <v>1.765</v>
-      </c>
-      <c r="P7">
-        <v>20</v>
-      </c>
-      <c r="Q7">
-        <v>58.7</v>
-      </c>
-      <c r="R7">
-        <v>0.571</v>
-      </c>
-      <c r="S7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8">
-        <v>86.01000000000001</v>
-      </c>
-      <c r="C8">
-        <v>3.517</v>
-      </c>
-      <c r="D8">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>99.964</v>
-      </c>
-      <c r="F8">
-        <v>0.094</v>
-      </c>
-      <c r="G8">
-        <v>20</v>
-      </c>
-      <c r="H8">
-        <v>537.6</v>
-      </c>
-      <c r="I8">
-        <v>91.175</v>
-      </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8">
-        <v>2215.25</v>
-      </c>
-      <c r="L8">
-        <v>51.058</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
-        <v>28.75</v>
-      </c>
-      <c r="O8">
-        <v>2.789</v>
-      </c>
-      <c r="P8">
-        <v>20</v>
-      </c>
-      <c r="Q8">
-        <v>58.75</v>
-      </c>
-      <c r="R8">
-        <v>0.55</v>
-      </c>
-      <c r="S8">
-        <v>20</v>
+    <row r="13" spans="1:21">
+      <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13">
+        <v>85.15600000000001</v>
+      </c>
+      <c r="C13">
+        <v>2.082</v>
+      </c>
+      <c r="D13">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>99.968</v>
+      </c>
+      <c r="F13">
+        <v>0.095</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>508.15</v>
+      </c>
+      <c r="I13">
+        <v>63.344</v>
+      </c>
+      <c r="J13">
+        <v>20</v>
+      </c>
+      <c r="K13">
+        <v>2227.6</v>
+      </c>
+      <c r="L13">
+        <v>37.252</v>
+      </c>
+      <c r="M13">
+        <v>20</v>
+      </c>
+      <c r="N13">
+        <v>27.7</v>
+      </c>
+      <c r="O13">
+        <v>2.203</v>
+      </c>
+      <c r="P13">
+        <v>20</v>
+      </c>
+      <c r="Q13">
+        <v>58.9</v>
+      </c>
+      <c r="R13">
+        <v>0.308</v>
+      </c>
+      <c r="S13">
+        <v>20</v>
+      </c>
+      <c r="T13" t="s">
+        <v>44</v>
+      </c>
+      <c r="U13" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
